--- a/output/pdf_financials_xlsx/CCA.xlsx
+++ b/output/pdf_financials_xlsx/CCA.xlsx
@@ -1279,7 +1279,7 @@
         <v>262.625</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>335.183</v>
+        <v>-180.317</v>
       </c>
       <c r="I16" s="3" t="n">
         <v>-120.485</v>
@@ -1579,7 +1579,7 @@
         <v>209.441</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>257.75</v>
+        <v>-257.75</v>
       </c>
       <c r="I20" s="3" t="n">
         <v>-189.628</v>
@@ -1753,7 +1753,7 @@
         <v>209.441</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>257.75</v>
+        <v>-257.75</v>
       </c>
       <c r="I23" s="3" t="n">
         <v>-189.628</v>
@@ -1937,7 +1937,7 @@
         <v>49.164554</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>49.377395</v>
+        <v>-49.377395</v>
       </c>
       <c r="I26" s="3" t="n">
         <v>48.999483</v>
@@ -1997,7 +1997,7 @@
         <v>262.625</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>335.183</v>
+        <v>-180.317</v>
       </c>
       <c r="I27" s="3" t="n">
         <v>-120.485</v>
@@ -2113,7 +2113,7 @@
         <v>722.907</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>801.898</v>
+        <v>286.398</v>
       </c>
       <c r="I29" s="3" t="n">
         <v>377.478</v>
@@ -2171,7 +2171,7 @@
         <v>37.11800886325722</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>39.24493323597525</v>
+        <v>14.01633423317783</v>
       </c>
       <c r="I30" s="3" t="n">
         <v>17.34614679417632</v>
@@ -2229,7 +2229,7 @@
         <v>20.25092812946216</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>23.10170861887387</v>
+        <v>-42.94270645585275</v>
       </c>
       <c r="I31" s="3" t="n">
         <v>-57.38722662572104</v>
@@ -2287,7 +2287,7 @@
         <v>10.75384924247442</v>
       </c>
       <c r="H32" s="3" t="n">
-        <v>12.61429950139871</v>
+        <v>-12.61429950139871</v>
       </c>
       <c r="I32" s="3" t="n">
         <v>-8.713925379190487</v>
@@ -5765,46 +5765,46 @@
         <v>6.471</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>9.749000000000001</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>10.884</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>11.28</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>12.535</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>13.328</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>13.086</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>15.26</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>13.526</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>16.347</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>16.889</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>19.965</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>19.896</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0</v>
+        <v>19.719</v>
       </c>
       <c r="R92" s="3" t="n">
-        <v>0</v>
+        <v>19.986</v>
       </c>
     </row>
     <row r="93">
@@ -6135,13 +6135,13 @@
         <v>209.441</v>
       </c>
       <c r="H99" s="3" t="n">
-        <v>257.75</v>
+        <v>-257.75</v>
       </c>
       <c r="I99" s="3" t="n">
         <v>-189.628</v>
       </c>
       <c r="J99" s="3" t="n">
-        <v>299.225</v>
+        <v>-299.225</v>
       </c>
       <c r="K99" s="3" t="n">
         <v>360.197</v>
@@ -10694,7 +10694,11 @@
           <t>Share-based payment reserve</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr"/>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E27" t="inlineStr">
         <is>
           <t>-</t>
@@ -15946,7 +15950,11 @@
           <t>Share-based payment reserve</t>
         </is>
       </c>
-      <c r="D81" t="inlineStr"/>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E81" t="inlineStr">
         <is>
           <t>-</t>
@@ -35659,13 +35667,13 @@
         </is>
       </c>
       <c r="K282" s="5" t="n">
-        <v>257.75</v>
+        <v>-257.75</v>
       </c>
       <c r="L282" s="5" t="n">
         <v>-189.628</v>
       </c>
       <c r="M282" s="5" t="n">
-        <v>299.225</v>
+        <v>-299.225</v>
       </c>
       <c r="N282" t="inlineStr">
         <is>
@@ -49702,7 +49710,7 @@
         <v>-45.571</v>
       </c>
       <c r="H426" s="5" t="n">
-        <v>224.963</v>
+        <v>-224.963</v>
       </c>
       <c r="I426" t="inlineStr">
         <is>
@@ -49715,13 +49723,13 @@
         </is>
       </c>
       <c r="K426" s="5" t="n">
-        <v>257.75</v>
+        <v>-257.75</v>
       </c>
       <c r="L426" s="5" t="n">
         <v>-189.628</v>
       </c>
       <c r="M426" s="5" t="n">
-        <v>299.225</v>
+        <v>-299.225</v>
       </c>
       <c r="N426" t="inlineStr">
         <is>
@@ -53824,7 +53832,7 @@
         <v>-0.00094</v>
       </c>
       <c r="H468" s="5" t="n">
-        <v>0.00462</v>
+        <v>-0.00462</v>
       </c>
       <c r="I468" t="inlineStr">
         <is>
@@ -54026,7 +54034,7 @@
         <v>-0.00094</v>
       </c>
       <c r="H470" s="5" t="n">
-        <v>0.0046</v>
+        <v>-0.0046</v>
       </c>
       <c r="I470" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/CCA.xlsx
+++ b/output/pdf_financials_xlsx/CCA.xlsx
@@ -6892,31 +6892,31 @@
         <v>0</v>
       </c>
       <c r="I112" s="3" t="n">
-        <v>0</v>
+        <v>2.635</v>
       </c>
       <c r="J112" s="3" t="n">
-        <v>0</v>
+        <v>9.648</v>
       </c>
       <c r="K112" s="3" t="n">
-        <v>0</v>
+        <v>1.383</v>
       </c>
       <c r="L112" s="3" t="n">
-        <v>0</v>
+        <v>2.343</v>
       </c>
       <c r="M112" s="3" t="n">
-        <v>0</v>
+        <v>8.224</v>
       </c>
       <c r="N112" s="3" t="n">
-        <v>0</v>
+        <v>2.458</v>
       </c>
       <c r="O112" s="3" t="n">
-        <v>0</v>
+        <v>2.906</v>
       </c>
       <c r="P112" s="3" t="n">
-        <v>0</v>
+        <v>2.651</v>
       </c>
       <c r="Q112" s="3" t="n">
-        <v>0</v>
+        <v>3.378</v>
       </c>
       <c r="R112" s="3" t="n">
         <v>0</v>
@@ -27994,7 +27994,11 @@
           <t>Proceeds on disposals of property, plant and equipment</t>
         </is>
       </c>
-      <c r="D203" t="inlineStr"/>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E203" t="inlineStr">
         <is>
           <t>-</t>
@@ -31761,7 +31765,11 @@
           <t>Proceeds on disposals of property, plant and equipment</t>
         </is>
       </c>
-      <c r="D242" t="inlineStr"/>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E242" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/CCA.xlsx
+++ b/output/pdf_financials_xlsx/CCA.xlsx
@@ -6123,7 +6123,7 @@
         <v>157.303</v>
       </c>
       <c r="D99" s="3" t="n">
-        <v>-45.571</v>
+        <v>-47.666</v>
       </c>
       <c r="E99" s="3" t="n">
         <v>224.963</v>
@@ -41846,7 +41846,11 @@
           <t>Net income (loss)</t>
         </is>
       </c>
-      <c r="D345" t="inlineStr"/>
+      <c r="D345" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E345" s="5" t="n">
         <v>-258.228</v>
       </c>
@@ -42242,7 +42246,11 @@
           <t>Future income taxes</t>
         </is>
       </c>
-      <c r="D349" t="inlineStr"/>
+      <c r="D349" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E349" s="5" t="n">
         <v>2.887</v>
       </c>
